--- a/TestData/TMTT0011413_Verify_the_time_entries_should_be_rounded_off_to_1_decimal_place_automatically.xlsx
+++ b/TestData/TMTT0011413_Verify_the_time_entries_should_be_rounded_off_to_1_decimal_place_automatically.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D16259D-F8E2-4141-B006-867F7429723E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A545F02-DF06-4B5F-8499-18E72EAA7CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
-    <sheet name="Project_Title" sheetId="15" r:id="rId2"/>
-    <sheet name="StaffMember" sheetId="11" r:id="rId3"/>
-    <sheet name="Update_Hours" sheetId="13" r:id="rId4"/>
-    <sheet name="Update_Timer" sheetId="16" r:id="rId5"/>
-    <sheet name="RateSheetManagement" sheetId="17" r:id="rId6"/>
-    <sheet name="WeeklyEntryMatrix" sheetId="14" r:id="rId7"/>
+    <sheet name="AppName" sheetId="18" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="19" r:id="rId3"/>
+    <sheet name="Project_Title" sheetId="15" r:id="rId4"/>
+    <sheet name="StaffMember" sheetId="11" r:id="rId5"/>
+    <sheet name="Update_Hours" sheetId="13" r:id="rId6"/>
+    <sheet name="Update_Timer" sheetId="16" r:id="rId7"/>
+    <sheet name="RateSheetManagement" sheetId="17" r:id="rId8"/>
+    <sheet name="WeeklyEntryMatrix" sheetId="14" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>Global Search User</t>
   </si>
@@ -85,6 +87,18 @@
   </si>
   <si>
     <t>Coartney Trone</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Time Record Manager</t>
   </si>
 </sst>
 </file>
@@ -815,6 +829,46 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDA4613-7B88-481B-977C-40459C2D867C}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86973ED2-A342-46D8-94B2-C16E55CE8685}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -847,7 +901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -870,7 +924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -890,7 +944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -916,7 +970,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -948,7 +1002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/TestData/TMTT0011413_Verify_the_time_entries_should_be_rounded_off_to_1_decimal_place_automatically.xlsx
+++ b/TestData/TMTT0011413_Verify_the_time_entries_should_be_rounded_off_to_1_decimal_place_automatically.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A545F02-DF06-4B5F-8499-18E72EAA7CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC4CE75-A54C-40EA-A598-3768B2AD45FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -910,7 +910,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
     </row>

--- a/TestData/TMTT0011413_Verify_the_time_entries_should_be_rounded_off_to_1_decimal_place_automatically.xlsx
+++ b/TestData/TMTT0011413_Verify_the_time_entries_should_be_rounded_off_to_1_decimal_place_automatically.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D16259D-F8E2-4141-B006-867F7429723E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC4CE75-A54C-40EA-A598-3768B2AD45FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
-    <sheet name="Project_Title" sheetId="15" r:id="rId2"/>
-    <sheet name="StaffMember" sheetId="11" r:id="rId3"/>
-    <sheet name="Update_Hours" sheetId="13" r:id="rId4"/>
-    <sheet name="Update_Timer" sheetId="16" r:id="rId5"/>
-    <sheet name="RateSheetManagement" sheetId="17" r:id="rId6"/>
-    <sheet name="WeeklyEntryMatrix" sheetId="14" r:id="rId7"/>
+    <sheet name="AppName" sheetId="18" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="19" r:id="rId3"/>
+    <sheet name="Project_Title" sheetId="15" r:id="rId4"/>
+    <sheet name="StaffMember" sheetId="11" r:id="rId5"/>
+    <sheet name="Update_Hours" sheetId="13" r:id="rId6"/>
+    <sheet name="Update_Timer" sheetId="16" r:id="rId7"/>
+    <sheet name="RateSheetManagement" sheetId="17" r:id="rId8"/>
+    <sheet name="WeeklyEntryMatrix" sheetId="14" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>Global Search User</t>
   </si>
@@ -85,6 +87,18 @@
   </si>
   <si>
     <t>Coartney Trone</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Time Record Manager</t>
   </si>
 </sst>
 </file>
@@ -815,6 +829,46 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDA4613-7B88-481B-977C-40459C2D867C}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86973ED2-A342-46D8-94B2-C16E55CE8685}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -847,7 +901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -856,7 +910,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -870,7 +924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -890,7 +944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -916,7 +970,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -948,7 +1002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
